--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260611.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.92%</t>
+          <t>10.61%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.27%</t>
+          <t>10.16%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>376,289,486</t>
+          <t>375,900,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.39%</t>
+          <t>6.42%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>4.94%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>109,574,000</t>
+          <t>111,074,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
@@ -721,56 +721,56 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>185,167,000</t>
+          <t>184,975,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>202606TX</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,401</t>
+          <t>4,995,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>202606TX</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,306</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>134,492,945</t>
+          <t>134,352,945</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -880,95 +880,95 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>28,522,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>28,864,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>30,366,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -990,24 +990,24 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>227,132,516</t>
+          <t>97,767,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>97,767,000</t>
+          <t>25,907,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>25,934,000</t>
+          <t>226,896,516</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>62,556,000</t>
+          <t>62,491,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -1100,90 +1100,90 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>178,956,000</t>
+          <t>329,875,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>178,956,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>324,375,000</t>
+          <t>49,497,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14,243,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>48,997,000</t>
+          <t>14,243,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,922,448,474</t>
+          <t>12,291,053,746</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,625,516,162</t>
+          <t>9,554,235,462</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-2,861,506,446</t>
+          <t>-1,980,568,897</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
